--- a/INSTANCES/instances_xlsx/A_MTN_5/224FL_10A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/224FL_10A_4.xlsx
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7658,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
